--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5924" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="2677">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5924" uniqueCount="2677">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -33252,7 +33252,7 @@
       <c r="J35">
         <v>19.99</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="K35" t="s">
         <v>503</v>
       </c>
       <c r="L35" t="s">
@@ -33657,27 +33657,26 @@
     <hyperlink ref="K34" r:id="rId63"/>
     <hyperlink ref="M34" r:id="rId64"/>
     <hyperlink ref="N34" r:id="rId65"/>
-    <hyperlink ref="K35" r:id="rId66"/>
-    <hyperlink ref="M35" r:id="rId67"/>
-    <hyperlink ref="N35" r:id="rId68"/>
-    <hyperlink ref="K36" r:id="rId69"/>
-    <hyperlink ref="M36" r:id="rId70"/>
-    <hyperlink ref="N36" r:id="rId71"/>
-    <hyperlink ref="K37" r:id="rId72"/>
-    <hyperlink ref="M37" r:id="rId73"/>
-    <hyperlink ref="N37" r:id="rId74"/>
-    <hyperlink ref="K38" r:id="rId75"/>
-    <hyperlink ref="M38" r:id="rId76"/>
-    <hyperlink ref="N38" r:id="rId77"/>
-    <hyperlink ref="K39" r:id="rId78"/>
-    <hyperlink ref="M39" r:id="rId79"/>
-    <hyperlink ref="N39" r:id="rId80"/>
-    <hyperlink ref="K40" r:id="rId81"/>
-    <hyperlink ref="M40" r:id="rId82"/>
-    <hyperlink ref="N40" r:id="rId83"/>
-    <hyperlink ref="K41" r:id="rId84"/>
-    <hyperlink ref="M41" r:id="rId85"/>
-    <hyperlink ref="N41" r:id="rId86"/>
+    <hyperlink ref="M35" r:id="rId66"/>
+    <hyperlink ref="N35" r:id="rId67"/>
+    <hyperlink ref="K36" r:id="rId68"/>
+    <hyperlink ref="M36" r:id="rId69"/>
+    <hyperlink ref="N36" r:id="rId70"/>
+    <hyperlink ref="K37" r:id="rId71"/>
+    <hyperlink ref="M37" r:id="rId72"/>
+    <hyperlink ref="N37" r:id="rId73"/>
+    <hyperlink ref="K38" r:id="rId74"/>
+    <hyperlink ref="M38" r:id="rId75"/>
+    <hyperlink ref="N38" r:id="rId76"/>
+    <hyperlink ref="K39" r:id="rId77"/>
+    <hyperlink ref="M39" r:id="rId78"/>
+    <hyperlink ref="N39" r:id="rId79"/>
+    <hyperlink ref="K40" r:id="rId80"/>
+    <hyperlink ref="M40" r:id="rId81"/>
+    <hyperlink ref="N40" r:id="rId82"/>
+    <hyperlink ref="K41" r:id="rId83"/>
+    <hyperlink ref="M41" r:id="rId84"/>
+    <hyperlink ref="N41" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5924" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="2677">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -33252,7 +33252,7 @@
       <c r="J35">
         <v>19.99</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="3" t="s">
         <v>503</v>
       </c>
       <c r="L35" t="s">
@@ -33657,26 +33657,27 @@
     <hyperlink ref="K34" r:id="rId63"/>
     <hyperlink ref="M34" r:id="rId64"/>
     <hyperlink ref="N34" r:id="rId65"/>
-    <hyperlink ref="M35" r:id="rId66"/>
-    <hyperlink ref="N35" r:id="rId67"/>
-    <hyperlink ref="K36" r:id="rId68"/>
-    <hyperlink ref="M36" r:id="rId69"/>
-    <hyperlink ref="N36" r:id="rId70"/>
-    <hyperlink ref="K37" r:id="rId71"/>
-    <hyperlink ref="M37" r:id="rId72"/>
-    <hyperlink ref="N37" r:id="rId73"/>
-    <hyperlink ref="K38" r:id="rId74"/>
-    <hyperlink ref="M38" r:id="rId75"/>
-    <hyperlink ref="N38" r:id="rId76"/>
-    <hyperlink ref="K39" r:id="rId77"/>
-    <hyperlink ref="M39" r:id="rId78"/>
-    <hyperlink ref="N39" r:id="rId79"/>
-    <hyperlink ref="K40" r:id="rId80"/>
-    <hyperlink ref="M40" r:id="rId81"/>
-    <hyperlink ref="N40" r:id="rId82"/>
-    <hyperlink ref="K41" r:id="rId83"/>
-    <hyperlink ref="M41" r:id="rId84"/>
-    <hyperlink ref="N41" r:id="rId85"/>
+    <hyperlink ref="K35" r:id="rId66"/>
+    <hyperlink ref="M35" r:id="rId67"/>
+    <hyperlink ref="N35" r:id="rId68"/>
+    <hyperlink ref="K36" r:id="rId69"/>
+    <hyperlink ref="M36" r:id="rId70"/>
+    <hyperlink ref="N36" r:id="rId71"/>
+    <hyperlink ref="K37" r:id="rId72"/>
+    <hyperlink ref="M37" r:id="rId73"/>
+    <hyperlink ref="N37" r:id="rId74"/>
+    <hyperlink ref="K38" r:id="rId75"/>
+    <hyperlink ref="M38" r:id="rId76"/>
+    <hyperlink ref="N38" r:id="rId77"/>
+    <hyperlink ref="K39" r:id="rId78"/>
+    <hyperlink ref="M39" r:id="rId79"/>
+    <hyperlink ref="N39" r:id="rId80"/>
+    <hyperlink ref="K40" r:id="rId81"/>
+    <hyperlink ref="M40" r:id="rId82"/>
+    <hyperlink ref="N40" r:id="rId83"/>
+    <hyperlink ref="K41" r:id="rId84"/>
+    <hyperlink ref="M41" r:id="rId85"/>
+    <hyperlink ref="N41" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5923" uniqueCount="2677">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -24055,7 +24055,7 @@
       <c r="J58">
         <v>19.99</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K58" t="s">
         <v>503</v>
       </c>
       <c r="L58" t="s">
@@ -24690,7 +24690,7 @@
       <c r="J71">
         <v>0</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="K71" t="s">
         <v>503</v>
       </c>
       <c r="L71" t="s">
@@ -25557,76 +25557,74 @@
     <hyperlink ref="N56" r:id="rId113"/>
     <hyperlink ref="M57" r:id="rId114"/>
     <hyperlink ref="N57" r:id="rId115"/>
-    <hyperlink ref="K58" r:id="rId116"/>
-    <hyperlink ref="M58" r:id="rId117"/>
-    <hyperlink ref="N58" r:id="rId118"/>
-    <hyperlink ref="M59" r:id="rId119"/>
-    <hyperlink ref="N59" r:id="rId120"/>
-    <hyperlink ref="K60" r:id="rId121"/>
-    <hyperlink ref="M60" r:id="rId122"/>
-    <hyperlink ref="N60" r:id="rId123"/>
-    <hyperlink ref="M61" r:id="rId124"/>
-    <hyperlink ref="N61" r:id="rId125"/>
-    <hyperlink ref="M62" r:id="rId126"/>
-    <hyperlink ref="N62" r:id="rId127"/>
-    <hyperlink ref="K63" r:id="rId128"/>
-    <hyperlink ref="M63" r:id="rId129"/>
-    <hyperlink ref="N63" r:id="rId130"/>
-    <hyperlink ref="M64" r:id="rId131"/>
-    <hyperlink ref="N64" r:id="rId132"/>
-    <hyperlink ref="K65" r:id="rId133"/>
-    <hyperlink ref="M65" r:id="rId134"/>
-    <hyperlink ref="N65" r:id="rId135"/>
-    <hyperlink ref="M66" r:id="rId136"/>
-    <hyperlink ref="N66" r:id="rId137"/>
-    <hyperlink ref="M67" r:id="rId138"/>
-    <hyperlink ref="N67" r:id="rId139"/>
-    <hyperlink ref="M68" r:id="rId140"/>
-    <hyperlink ref="N68" r:id="rId141"/>
-    <hyperlink ref="K69" r:id="rId142"/>
-    <hyperlink ref="M69" r:id="rId143"/>
-    <hyperlink ref="N69" r:id="rId144"/>
-    <hyperlink ref="K70" r:id="rId145"/>
-    <hyperlink ref="M70" r:id="rId146"/>
-    <hyperlink ref="N70" r:id="rId147"/>
-    <hyperlink ref="K71" r:id="rId148"/>
-    <hyperlink ref="M71" r:id="rId149"/>
-    <hyperlink ref="N71" r:id="rId150"/>
-    <hyperlink ref="K72" r:id="rId151"/>
-    <hyperlink ref="M72" r:id="rId152"/>
-    <hyperlink ref="N72" r:id="rId153"/>
-    <hyperlink ref="K73" r:id="rId154"/>
-    <hyperlink ref="M73" r:id="rId155"/>
-    <hyperlink ref="N73" r:id="rId156"/>
-    <hyperlink ref="K74" r:id="rId157"/>
-    <hyperlink ref="M74" r:id="rId158"/>
-    <hyperlink ref="N74" r:id="rId159"/>
-    <hyperlink ref="M75" r:id="rId160"/>
-    <hyperlink ref="N75" r:id="rId161"/>
-    <hyperlink ref="K76" r:id="rId162"/>
-    <hyperlink ref="M76" r:id="rId163"/>
-    <hyperlink ref="N76" r:id="rId164"/>
-    <hyperlink ref="K77" r:id="rId165"/>
-    <hyperlink ref="M77" r:id="rId166"/>
-    <hyperlink ref="N77" r:id="rId167"/>
-    <hyperlink ref="M78" r:id="rId168"/>
-    <hyperlink ref="N78" r:id="rId169"/>
-    <hyperlink ref="M79" r:id="rId170"/>
-    <hyperlink ref="N79" r:id="rId171"/>
-    <hyperlink ref="K80" r:id="rId172"/>
-    <hyperlink ref="M80" r:id="rId173"/>
-    <hyperlink ref="N80" r:id="rId174"/>
-    <hyperlink ref="M81" r:id="rId175"/>
-    <hyperlink ref="N81" r:id="rId176"/>
-    <hyperlink ref="M82" r:id="rId177"/>
-    <hyperlink ref="N82" r:id="rId178"/>
-    <hyperlink ref="K83" r:id="rId179"/>
-    <hyperlink ref="M83" r:id="rId180"/>
-    <hyperlink ref="N83" r:id="rId181"/>
-    <hyperlink ref="M84" r:id="rId182"/>
-    <hyperlink ref="N84" r:id="rId183"/>
-    <hyperlink ref="M85" r:id="rId184"/>
-    <hyperlink ref="N85" r:id="rId185"/>
+    <hyperlink ref="M58" r:id="rId116"/>
+    <hyperlink ref="N58" r:id="rId117"/>
+    <hyperlink ref="M59" r:id="rId118"/>
+    <hyperlink ref="N59" r:id="rId119"/>
+    <hyperlink ref="K60" r:id="rId120"/>
+    <hyperlink ref="M60" r:id="rId121"/>
+    <hyperlink ref="N60" r:id="rId122"/>
+    <hyperlink ref="M61" r:id="rId123"/>
+    <hyperlink ref="N61" r:id="rId124"/>
+    <hyperlink ref="M62" r:id="rId125"/>
+    <hyperlink ref="N62" r:id="rId126"/>
+    <hyperlink ref="K63" r:id="rId127"/>
+    <hyperlink ref="M63" r:id="rId128"/>
+    <hyperlink ref="N63" r:id="rId129"/>
+    <hyperlink ref="M64" r:id="rId130"/>
+    <hyperlink ref="N64" r:id="rId131"/>
+    <hyperlink ref="K65" r:id="rId132"/>
+    <hyperlink ref="M65" r:id="rId133"/>
+    <hyperlink ref="N65" r:id="rId134"/>
+    <hyperlink ref="M66" r:id="rId135"/>
+    <hyperlink ref="N66" r:id="rId136"/>
+    <hyperlink ref="M67" r:id="rId137"/>
+    <hyperlink ref="N67" r:id="rId138"/>
+    <hyperlink ref="M68" r:id="rId139"/>
+    <hyperlink ref="N68" r:id="rId140"/>
+    <hyperlink ref="K69" r:id="rId141"/>
+    <hyperlink ref="M69" r:id="rId142"/>
+    <hyperlink ref="N69" r:id="rId143"/>
+    <hyperlink ref="K70" r:id="rId144"/>
+    <hyperlink ref="M70" r:id="rId145"/>
+    <hyperlink ref="N70" r:id="rId146"/>
+    <hyperlink ref="M71" r:id="rId147"/>
+    <hyperlink ref="N71" r:id="rId148"/>
+    <hyperlink ref="K72" r:id="rId149"/>
+    <hyperlink ref="M72" r:id="rId150"/>
+    <hyperlink ref="N72" r:id="rId151"/>
+    <hyperlink ref="K73" r:id="rId152"/>
+    <hyperlink ref="M73" r:id="rId153"/>
+    <hyperlink ref="N73" r:id="rId154"/>
+    <hyperlink ref="K74" r:id="rId155"/>
+    <hyperlink ref="M74" r:id="rId156"/>
+    <hyperlink ref="N74" r:id="rId157"/>
+    <hyperlink ref="M75" r:id="rId158"/>
+    <hyperlink ref="N75" r:id="rId159"/>
+    <hyperlink ref="K76" r:id="rId160"/>
+    <hyperlink ref="M76" r:id="rId161"/>
+    <hyperlink ref="N76" r:id="rId162"/>
+    <hyperlink ref="K77" r:id="rId163"/>
+    <hyperlink ref="M77" r:id="rId164"/>
+    <hyperlink ref="N77" r:id="rId165"/>
+    <hyperlink ref="M78" r:id="rId166"/>
+    <hyperlink ref="N78" r:id="rId167"/>
+    <hyperlink ref="M79" r:id="rId168"/>
+    <hyperlink ref="N79" r:id="rId169"/>
+    <hyperlink ref="K80" r:id="rId170"/>
+    <hyperlink ref="M80" r:id="rId171"/>
+    <hyperlink ref="N80" r:id="rId172"/>
+    <hyperlink ref="M81" r:id="rId173"/>
+    <hyperlink ref="N81" r:id="rId174"/>
+    <hyperlink ref="M82" r:id="rId175"/>
+    <hyperlink ref="N82" r:id="rId176"/>
+    <hyperlink ref="K83" r:id="rId177"/>
+    <hyperlink ref="M83" r:id="rId178"/>
+    <hyperlink ref="N83" r:id="rId179"/>
+    <hyperlink ref="M84" r:id="rId180"/>
+    <hyperlink ref="N84" r:id="rId181"/>
+    <hyperlink ref="M85" r:id="rId182"/>
+    <hyperlink ref="N85" r:id="rId183"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/MOTU/lista_MOTU.xlsx
+++ b/data/MOTU/lista_MOTU.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5923" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="2677">
   <si>
     <t>Origins Action Figures Checklist</t>
   </si>
@@ -24055,7 +24055,7 @@
       <c r="J58">
         <v>19.99</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="3" t="s">
         <v>503</v>
       </c>
       <c r="L58" t="s">
@@ -24690,7 +24690,7 @@
       <c r="J71">
         <v>0</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K71" s="3" t="s">
         <v>503</v>
       </c>
       <c r="L71" t="s">
@@ -25557,74 +25557,76 @@
     <hyperlink ref="N56" r:id="rId113"/>
     <hyperlink ref="M57" r:id="rId114"/>
     <hyperlink ref="N57" r:id="rId115"/>
-    <hyperlink ref="M58" r:id="rId116"/>
-    <hyperlink ref="N58" r:id="rId117"/>
-    <hyperlink ref="M59" r:id="rId118"/>
-    <hyperlink ref="N59" r:id="rId119"/>
-    <hyperlink ref="K60" r:id="rId120"/>
-    <hyperlink ref="M60" r:id="rId121"/>
-    <hyperlink ref="N60" r:id="rId122"/>
-    <hyperlink ref="M61" r:id="rId123"/>
-    <hyperlink ref="N61" r:id="rId124"/>
-    <hyperlink ref="M62" r:id="rId125"/>
-    <hyperlink ref="N62" r:id="rId126"/>
-    <hyperlink ref="K63" r:id="rId127"/>
-    <hyperlink ref="M63" r:id="rId128"/>
-    <hyperlink ref="N63" r:id="rId129"/>
-    <hyperlink ref="M64" r:id="rId130"/>
-    <hyperlink ref="N64" r:id="rId131"/>
-    <hyperlink ref="K65" r:id="rId132"/>
-    <hyperlink ref="M65" r:id="rId133"/>
-    <hyperlink ref="N65" r:id="rId134"/>
-    <hyperlink ref="M66" r:id="rId135"/>
-    <hyperlink ref="N66" r:id="rId136"/>
-    <hyperlink ref="M67" r:id="rId137"/>
-    <hyperlink ref="N67" r:id="rId138"/>
-    <hyperlink ref="M68" r:id="rId139"/>
-    <hyperlink ref="N68" r:id="rId140"/>
-    <hyperlink ref="K69" r:id="rId141"/>
-    <hyperlink ref="M69" r:id="rId142"/>
-    <hyperlink ref="N69" r:id="rId143"/>
-    <hyperlink ref="K70" r:id="rId144"/>
-    <hyperlink ref="M70" r:id="rId145"/>
-    <hyperlink ref="N70" r:id="rId146"/>
-    <hyperlink ref="M71" r:id="rId147"/>
-    <hyperlink ref="N71" r:id="rId148"/>
-    <hyperlink ref="K72" r:id="rId149"/>
-    <hyperlink ref="M72" r:id="rId150"/>
-    <hyperlink ref="N72" r:id="rId151"/>
-    <hyperlink ref="K73" r:id="rId152"/>
-    <hyperlink ref="M73" r:id="rId153"/>
-    <hyperlink ref="N73" r:id="rId154"/>
-    <hyperlink ref="K74" r:id="rId155"/>
-    <hyperlink ref="M74" r:id="rId156"/>
-    <hyperlink ref="N74" r:id="rId157"/>
-    <hyperlink ref="M75" r:id="rId158"/>
-    <hyperlink ref="N75" r:id="rId159"/>
-    <hyperlink ref="K76" r:id="rId160"/>
-    <hyperlink ref="M76" r:id="rId161"/>
-    <hyperlink ref="N76" r:id="rId162"/>
-    <hyperlink ref="K77" r:id="rId163"/>
-    <hyperlink ref="M77" r:id="rId164"/>
-    <hyperlink ref="N77" r:id="rId165"/>
-    <hyperlink ref="M78" r:id="rId166"/>
-    <hyperlink ref="N78" r:id="rId167"/>
-    <hyperlink ref="M79" r:id="rId168"/>
-    <hyperlink ref="N79" r:id="rId169"/>
-    <hyperlink ref="K80" r:id="rId170"/>
-    <hyperlink ref="M80" r:id="rId171"/>
-    <hyperlink ref="N80" r:id="rId172"/>
-    <hyperlink ref="M81" r:id="rId173"/>
-    <hyperlink ref="N81" r:id="rId174"/>
-    <hyperlink ref="M82" r:id="rId175"/>
-    <hyperlink ref="N82" r:id="rId176"/>
-    <hyperlink ref="K83" r:id="rId177"/>
-    <hyperlink ref="M83" r:id="rId178"/>
-    <hyperlink ref="N83" r:id="rId179"/>
-    <hyperlink ref="M84" r:id="rId180"/>
-    <hyperlink ref="N84" r:id="rId181"/>
-    <hyperlink ref="M85" r:id="rId182"/>
-    <hyperlink ref="N85" r:id="rId183"/>
+    <hyperlink ref="K58" r:id="rId116"/>
+    <hyperlink ref="M58" r:id="rId117"/>
+    <hyperlink ref="N58" r:id="rId118"/>
+    <hyperlink ref="M59" r:id="rId119"/>
+    <hyperlink ref="N59" r:id="rId120"/>
+    <hyperlink ref="K60" r:id="rId121"/>
+    <hyperlink ref="M60" r:id="rId122"/>
+    <hyperlink ref="N60" r:id="rId123"/>
+    <hyperlink ref="M61" r:id="rId124"/>
+    <hyperlink ref="N61" r:id="rId125"/>
+    <hyperlink ref="M62" r:id="rId126"/>
+    <hyperlink ref="N62" r:id="rId127"/>
+    <hyperlink ref="K63" r:id="rId128"/>
+    <hyperlink ref="M63" r:id="rId129"/>
+    <hyperlink ref="N63" r:id="rId130"/>
+    <hyperlink ref="M64" r:id="rId131"/>
+    <hyperlink ref="N64" r:id="rId132"/>
+    <hyperlink ref="K65" r:id="rId133"/>
+    <hyperlink ref="M65" r:id="rId134"/>
+    <hyperlink ref="N65" r:id="rId135"/>
+    <hyperlink ref="M66" r:id="rId136"/>
+    <hyperlink ref="N66" r:id="rId137"/>
+    <hyperlink ref="M67" r:id="rId138"/>
+    <hyperlink ref="N67" r:id="rId139"/>
+    <hyperlink ref="M68" r:id="rId140"/>
+    <hyperlink ref="N68" r:id="rId141"/>
+    <hyperlink ref="K69" r:id="rId142"/>
+    <hyperlink ref="M69" r:id="rId143"/>
+    <hyperlink ref="N69" r:id="rId144"/>
+    <hyperlink ref="K70" r:id="rId145"/>
+    <hyperlink ref="M70" r:id="rId146"/>
+    <hyperlink ref="N70" r:id="rId147"/>
+    <hyperlink ref="K71" r:id="rId148"/>
+    <hyperlink ref="M71" r:id="rId149"/>
+    <hyperlink ref="N71" r:id="rId150"/>
+    <hyperlink ref="K72" r:id="rId151"/>
+    <hyperlink ref="M72" r:id="rId152"/>
+    <hyperlink ref="N72" r:id="rId153"/>
+    <hyperlink ref="K73" r:id="rId154"/>
+    <hyperlink ref="M73" r:id="rId155"/>
+    <hyperlink ref="N73" r:id="rId156"/>
+    <hyperlink ref="K74" r:id="rId157"/>
+    <hyperlink ref="M74" r:id="rId158"/>
+    <hyperlink ref="N74" r:id="rId159"/>
+    <hyperlink ref="M75" r:id="rId160"/>
+    <hyperlink ref="N75" r:id="rId161"/>
+    <hyperlink ref="K76" r:id="rId162"/>
+    <hyperlink ref="M76" r:id="rId163"/>
+    <hyperlink ref="N76" r:id="rId164"/>
+    <hyperlink ref="K77" r:id="rId165"/>
+    <hyperlink ref="M77" r:id="rId166"/>
+    <hyperlink ref="N77" r:id="rId167"/>
+    <hyperlink ref="M78" r:id="rId168"/>
+    <hyperlink ref="N78" r:id="rId169"/>
+    <hyperlink ref="M79" r:id="rId170"/>
+    <hyperlink ref="N79" r:id="rId171"/>
+    <hyperlink ref="K80" r:id="rId172"/>
+    <hyperlink ref="M80" r:id="rId173"/>
+    <hyperlink ref="N80" r:id="rId174"/>
+    <hyperlink ref="M81" r:id="rId175"/>
+    <hyperlink ref="N81" r:id="rId176"/>
+    <hyperlink ref="M82" r:id="rId177"/>
+    <hyperlink ref="N82" r:id="rId178"/>
+    <hyperlink ref="K83" r:id="rId179"/>
+    <hyperlink ref="M83" r:id="rId180"/>
+    <hyperlink ref="N83" r:id="rId181"/>
+    <hyperlink ref="M84" r:id="rId182"/>
+    <hyperlink ref="N84" r:id="rId183"/>
+    <hyperlink ref="M85" r:id="rId184"/>
+    <hyperlink ref="N85" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
